--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter3.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter3.xlsx
@@ -556,12 +556,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Player_Sick</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Player_Sick</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -601,7 +601,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Player_Sick</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -640,12 +640,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Player_Sick</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Player_Sick</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -677,7 +677,7 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Player_Sick</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Player_Sick</t>
+          <t>Player_Embarrassed</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -877,7 +877,7 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Player_Surprised</t>
+          <t>Player_Normal</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter3.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter3.xlsx
@@ -554,11 +554,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Player_Embarrassed</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Player_Embarrassed</t>
@@ -594,11 +590,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Panic</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Player_Embarrassed</t>
@@ -638,11 +630,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Player_Embarrassed</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Player_Embarrassed</t>
@@ -834,11 +822,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Shock</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -914,11 +898,7 @@
           <t>Dionysus</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Dionysus_Normal</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -962,11 +942,7 @@
           <t>Dionysus</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Dionysus_Smile</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -1042,11 +1018,7 @@
           <t>Dionysus</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Dionysus_Normal</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -1090,11 +1062,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Proud</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -1138,11 +1106,7 @@
           <t>Dionysus</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Dionysus_Smile</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
